--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,11 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Archivo</t>
         </is>
@@ -425,6 +430,11 @@
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>factura_001.pdf</t>
         </is>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,16 +427,164 @@
           <t>Archivo</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Importe_11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>factura_001.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Subtotal:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ubtotal:</t>
         </is>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,40 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Numero</t>
+          <t>Concepto</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Archivo</t>
+          <t>Cantidad</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Importe_11</t>
+          <t>Importe</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>factura_001.pdf</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>109,15 €</t>
@@ -454,137 +460,340 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>87,73 €</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>37,64 €</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>85,91 €</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>29,88 €</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>86,90 €</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Subtotal:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TENCIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ubtotal:</t>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
         </is>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3254,6 +3254,552 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,316 +413,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Codigo_Reserva</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fechas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>Apartamento Juan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>109,15 €</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>87,73 €</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>37,64 €</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>85,91 €</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29,88 €</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>86,90 €</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>759,53 €</t>
+          <t>Málaga) Ref Reser</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RETENCIÓN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BASE</t>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>759,53 €</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>759,53 €</t>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>RESERVA 31682853 (27/04/2026 - 04/05/2026)</t>
-        </is>
-      </c>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RESERVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>0,00 €</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>RESERVA 31682853 (27/04/2026 - 04/05/2026)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,20 +424,10 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Codigo_Reserva</t>
+          <t>Importe</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>Fechas</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Importe</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
@@ -449,12 +439,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -466,14 +454,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>109,15 €</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -485,14 +471,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -502,14 +486,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -521,12 +503,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -538,14 +518,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>87,73 €</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -557,14 +535,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -574,14 +550,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -593,12 +567,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -610,14 +582,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>37,64 €</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -629,14 +599,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -646,14 +614,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -665,12 +631,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -682,14 +646,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>85,91 €</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -701,14 +663,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -718,14 +678,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -737,12 +695,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -754,14 +710,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>29,88 €</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -773,14 +727,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -790,14 +742,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -809,12 +759,10 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -826,14 +774,12 @@
           <t>VFT/MA/68372) (Di</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>86,90 €</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -845,14 +791,12 @@
           <t>Málaga) Ref Reser</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RESERVA</t>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
@@ -862,14 +806,12 @@
           <t>LIMPIEZA FINAL</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
@@ -877,14 +819,12 @@
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>759,53 €</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -896,14 +836,12 @@
           <t>BASE</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>RETENCIÓN</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -915,14 +853,12 @@
           <t>759,53 €</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0,00 €</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
@@ -930,14 +866,3120 @@
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0,00 €</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>VFT/MA/68372) (Di</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Málaga) Ref Reser</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>LIMPIEZA FINAL</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,54 +424,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Importe</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109,15 €</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,47 +495,67 @@
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87,73 €</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Málaga) Ref Reser</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LIMPIEZA FINAL</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -529,49 +565,65 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VFT/MA/68372) (Di</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>37,64 €</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Málaga) Ref Reser</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Limpieza final</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LIMPIEZA FINAL</t>
+          <t>Limpieza final</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -581,209 +633,9 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Apartamento Juan</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>85,91 €</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Málaga) Ref Reser</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LIMPIEZA FINAL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMPIEZA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Apartamento Juan</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>29,88 €</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Málaga) Ref Reser</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LIMPIEZA FINAL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LIMPIEZA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Apartamento Juan</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VFT/MA/68372) (Di</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>86,90 €</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Málaga) Ref Reser</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LIMPIEZA FINAL</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LIMPIEZA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>759,53 €</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>RETENCIÓN</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>759,53 €</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>53,72 €</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,206 +434,562 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
         <is>
           <t>53,72 €</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Limpieza final</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
         </is>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,295 +435,217 @@
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>0</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>109,15 €</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
-        <v>0</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="n">
-        <v>0</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>87,73 €</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>37,64 €</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>85,91 €</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>29,88 €</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>86,90 €</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0,00 €</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>53,72 €</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>759,53 €</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0,00 €</t>
+          <t>RETENCIÓN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -732,9 +654,7 @@
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -748,9 +668,7 @@
           <t>Apartamento Juan</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -772,9 +690,7 @@
           <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -796,9 +712,7 @@
           <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -816,9 +730,7 @@
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -832,9 +744,7 @@
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -848,9 +758,7 @@
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -864,9 +772,7 @@
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -880,9 +786,7 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -896,9 +800,7 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -912,9 +814,7 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -928,9 +828,7 @@
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -944,9 +842,7 @@
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -993,6 +889,666 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>109,15 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>87,73 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>37,64 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>85,91 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>29,88 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>86,90 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>759,53 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>RETENCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,21 +434,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Apartamento Juan</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>109,15 €</t>
@@ -456,43 +456,39 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>87,73 €</t>
@@ -507,11 +503,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -535,11 +527,7 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -563,11 +551,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -591,11 +575,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -619,11 +599,7 @@
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -662,19 +638,27 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -684,41 +668,53 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -729,26 +725,38 @@
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>37,64 €</t>
@@ -757,26 +765,38 @@
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>85,91 €</t>
@@ -785,26 +805,38 @@
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>29,88 €</t>
@@ -813,26 +845,38 @@
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>86,90 €</t>
@@ -841,21 +885,29 @@
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>759,53 €</t>
@@ -864,7 +916,11 @@
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>RETENCIÓN</t>
@@ -873,7 +929,11 @@
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -882,7 +942,11 @@
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -890,19 +954,27 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -912,41 +984,53 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -957,26 +1041,38 @@
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>37,64 €</t>
@@ -985,26 +1081,38 @@
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>85,91 €</t>
@@ -1013,26 +1121,38 @@
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>29,88 €</t>
@@ -1041,26 +1161,38 @@
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>86,90 €</t>
@@ -1069,21 +1201,29 @@
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>759,53 €</t>
@@ -1092,7 +1232,11 @@
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>RETENCIÓN</t>
@@ -1101,7 +1245,11 @@
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -1110,7 +1258,11 @@
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>['53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €', '53,72 €']</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -1118,19 +1270,27 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1140,41 +1300,53 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1185,26 +1357,38 @@
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
           <t>37,64 €</t>
@@ -1213,26 +1397,38 @@
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>85,91 €</t>
@@ -1241,26 +1437,38 @@
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>29,88 €</t>
@@ -1269,26 +1477,38 @@
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>86,90 €</t>
@@ -1297,21 +1517,29 @@
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>53,72 €</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
           <t>759,53 €</t>
@@ -1320,7 +1548,11 @@
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
           <t>RETENCIÓN</t>
@@ -1329,7 +1561,11 @@
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -1338,7 +1574,11 @@
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -1346,19 +1586,27 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Apartamento Juan</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apartamento Juan</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31811373 (16/05/2026 - 21/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -1368,37 +1616,53 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ref Reserva: 31878061 (08/05/2026 - 10/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32119581 (21/05/2026 - 26/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32126242 (14/05/2026 - 16/05/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+          <t>53,72 €</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -1409,22 +1673,38 @@
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>37,64 €</t>
@@ -1433,22 +1713,38 @@
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
           <t>85,91 €</t>
@@ -1457,22 +1753,38 @@
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>29,88 €</t>
@@ -1481,22 +1793,38 @@
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>86,90 €</t>
@@ -1505,17 +1833,29 @@
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>759,53 €</t>
@@ -1524,7 +1864,11 @@
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
           <t>RETENCIÓN</t>
@@ -1533,7 +1877,11 @@
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>0,00 €</t>
@@ -1542,8 +1890,25 @@
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
+        <is>
+          <t>0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>53,72 €</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>0,00 €</t>
         </is>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="10">
   <si>
     <t>Concepto</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Ref Reserva: 32373942 (26/05/2026 - 01/06/2026)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -50,8 +53,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -79,9 +90,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
@@ -401,7 +413,7 @@
         <v>53.72</v>
       </c>
       <c r="C2" s="1">
-        <v>109.15</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -460,632 +472,349 @@
       </c>
     </row>
     <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>53.72</v>
+      </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>53.72</v>
       </c>
       <c r="C9" s="1">
-        <v>109.15</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>53.72</v>
       </c>
       <c r="C10" s="1">
-        <v>87.73</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>53.72</v>
       </c>
       <c r="C11" s="1">
-        <v>37.64</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>53.72</v>
       </c>
       <c r="C12" s="1">
-        <v>85.91</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>53.72</v>
       </c>
       <c r="C13" s="1">
-        <v>29.88</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>53.72</v>
       </c>
       <c r="C14" s="1">
-        <v>86.90000000000001</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15">
         <v>53.72</v>
       </c>
       <c r="C15" s="1">
-        <v>109.15</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16">
         <v>53.72</v>
       </c>
       <c r="C16" s="1">
-        <v>87.73</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17">
         <v>53.72</v>
       </c>
       <c r="C17" s="1">
-        <v>37.64</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>53.72</v>
       </c>
       <c r="C18" s="1">
-        <v>85.91</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>53.72</v>
       </c>
       <c r="C19" s="1">
-        <v>29.88</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B20">
         <v>53.72</v>
       </c>
       <c r="C20" s="1">
-        <v>86.90000000000001</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21">
         <v>53.72</v>
       </c>
       <c r="C21" s="1">
-        <v>109.15</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>53.72</v>
       </c>
       <c r="C22" s="1">
-        <v>87.73</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23">
         <v>53.72</v>
       </c>
       <c r="C23" s="1">
-        <v>37.64</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24">
         <v>53.72</v>
       </c>
       <c r="C24" s="1">
-        <v>85.91</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B25">
         <v>53.72</v>
       </c>
       <c r="C25" s="1">
-        <v>29.88</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B26">
         <v>53.72</v>
       </c>
       <c r="C26" s="1">
-        <v>86.90000000000001</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>53.72</v>
+      </c>
       <c r="C27" s="1">
-        <v>0</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>53.72</v>
       </c>
       <c r="C28" s="1">
-        <v>109.15</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>53.72</v>
       </c>
       <c r="C29" s="1">
-        <v>87.73</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B30">
         <v>53.72</v>
       </c>
       <c r="C30" s="1">
-        <v>37.64</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>53.72</v>
       </c>
       <c r="C31" s="1">
-        <v>85.91</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32">
-        <v>53.72</v>
+      <c r="B32" t="s">
+        <v>9</v>
       </c>
       <c r="C32" s="1">
-        <v>29.88</v>
+        <v>2298.9</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B33">
         <v>53.72</v>
       </c>
       <c r="C33" s="1">
-        <v>86.90000000000001</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34">
+        <v>53.72</v>
+      </c>
       <c r="C34" s="1">
-        <v>0</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B35">
         <v>53.72</v>
       </c>
       <c r="C35" s="1">
-        <v>2</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>53.72</v>
       </c>
       <c r="C36" s="1">
-        <v>3</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37">
         <v>53.72</v>
       </c>
       <c r="C37" s="1">
-        <v>37.64</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B38">
         <v>53.72</v>
       </c>
       <c r="C38" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39">
-        <v>53.72</v>
-      </c>
-      <c r="C39" s="1">
-        <v>29.88</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40">
-        <v>53.72</v>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C40" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="C41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42">
-        <v>53.72</v>
-      </c>
-      <c r="C42" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43">
-        <v>53.72</v>
-      </c>
-      <c r="C43" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44">
-        <v>53.72</v>
-      </c>
-      <c r="C44" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45">
-        <v>53.72</v>
-      </c>
-      <c r="C45" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46">
-        <v>53.72</v>
-      </c>
-      <c r="C46" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47">
-        <v>53.72</v>
-      </c>
-      <c r="C47" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="C48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49">
-        <v>53.72</v>
-      </c>
-      <c r="C49" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50">
-        <v>53.72</v>
-      </c>
-      <c r="C50" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51">
-        <v>53.72</v>
-      </c>
-      <c r="C51" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52">
-        <v>53.72</v>
-      </c>
-      <c r="C52" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53">
-        <v>53.72</v>
-      </c>
-      <c r="C53" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54">
-        <v>53.72</v>
-      </c>
-      <c r="C54" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="C55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56">
-        <v>53.72</v>
-      </c>
-      <c r="C56" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57">
-        <v>53.72</v>
-      </c>
-      <c r="C57" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58">
-        <v>53.72</v>
-      </c>
-      <c r="C58" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59">
-        <v>53.72</v>
-      </c>
-      <c r="C59" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60">
-        <v>53.72</v>
-      </c>
-      <c r="C60" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>8</v>
-      </c>
-      <c r="B61">
-        <v>53.72</v>
-      </c>
-      <c r="C61" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="C62" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63">
-        <v>53.72</v>
-      </c>
-      <c r="C63" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64">
-        <v>53.72</v>
-      </c>
-      <c r="C64" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>5</v>
-      </c>
-      <c r="B65">
-        <v>53.72</v>
-      </c>
-      <c r="C65" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66">
-        <v>53.72</v>
-      </c>
-      <c r="C66" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67">
-        <v>53.72</v>
-      </c>
-      <c r="C67" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68">
-        <v>53.72</v>
-      </c>
-      <c r="C68" s="1">
-        <f>SUM(C2:C67)</f>
+        <f>SUM(C2:C38)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Concepto</t>
   </si>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
@@ -413,7 +413,7 @@
         <v>53.72</v>
       </c>
       <c r="C2" s="1">
-        <v>222</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -538,283 +538,11 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>53.72</v>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C14" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>53.72</v>
-      </c>
-      <c r="C15" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>53.72</v>
-      </c>
-      <c r="C16" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>53.72</v>
-      </c>
-      <c r="C17" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <v>53.72</v>
-      </c>
-      <c r="C18" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19">
-        <v>53.72</v>
-      </c>
-      <c r="C19" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>53.72</v>
-      </c>
-      <c r="C20" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21">
-        <v>53.72</v>
-      </c>
-      <c r="C21" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22">
-        <v>53.72</v>
-      </c>
-      <c r="C22" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23">
-        <v>53.72</v>
-      </c>
-      <c r="C23" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24">
-        <v>53.72</v>
-      </c>
-      <c r="C24" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25">
-        <v>53.72</v>
-      </c>
-      <c r="C25" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26">
-        <v>53.72</v>
-      </c>
-      <c r="C26" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>53.72</v>
-      </c>
-      <c r="C27" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28">
-        <v>53.72</v>
-      </c>
-      <c r="C28" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29">
-        <v>53.72</v>
-      </c>
-      <c r="C29" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30">
-        <v>53.72</v>
-      </c>
-      <c r="C30" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31">
-        <v>53.72</v>
-      </c>
-      <c r="C31" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2298.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33">
-        <v>53.72</v>
-      </c>
-      <c r="C33" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34">
-        <v>53.72</v>
-      </c>
-      <c r="C34" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35">
-        <v>53.72</v>
-      </c>
-      <c r="C35" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36">
-        <v>53.72</v>
-      </c>
-      <c r="C36" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37">
-        <v>53.72</v>
-      </c>
-      <c r="C37" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38">
-        <v>53.72</v>
-      </c>
-      <c r="C38" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="B40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="1">
-        <f>SUM(C2:C38)</f>
+        <f>SUM(C2:C1000)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
   <si>
     <t>Concepto</t>
   </si>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
@@ -413,7 +413,7 @@
         <v>53.72</v>
       </c>
       <c r="C2" s="1">
-        <v>109.15</v>
+        <v>1029.15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -538,11 +538,77 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="B14" s="2" t="s">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>53.72</v>
+      </c>
+      <c r="C14" s="1">
+        <v>109.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>53.72</v>
+      </c>
+      <c r="C15" s="1">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>53.72</v>
+      </c>
+      <c r="C16" s="1">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>53.72</v>
+      </c>
+      <c r="C17" s="1">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>53.72</v>
+      </c>
+      <c r="C18" s="1">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>53.72</v>
+      </c>
+      <c r="C19" s="1">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="1">
-        <f>SUM(C2:C1000)</f>
+      <c r="C21" s="1">
+        <f>SUM(C2:C19)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="10">
   <si>
     <t>Concepto</t>
   </si>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
@@ -413,7 +413,7 @@
         <v>53.72</v>
       </c>
       <c r="C2" s="1">
-        <v>1029.15</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -603,12 +603,86 @@
         <v>86.90000000000001</v>
       </c>
     </row>
+    <row r="20" spans="1:3">
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1311.63</v>
+      </c>
+    </row>
     <row r="21" spans="1:3">
-      <c r="B21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>53.72</v>
+      </c>
+      <c r="C21" s="1">
+        <v>109.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>53.72</v>
+      </c>
+      <c r="C22" s="1">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>53.72</v>
+      </c>
+      <c r="C23" s="1">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>53.72</v>
+      </c>
+      <c r="C24" s="1">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>53.72</v>
+      </c>
+      <c r="C25" s="1">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>53.72</v>
+      </c>
+      <c r="C26" s="1">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="1">
-        <f>SUM(C2:C19)</f>
+      <c r="C28" s="1">
+        <f>SUM(C2:C26)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Concepto</t>
+  </si>
+  <si>
+    <t>Noches</t>
   </si>
   <si>
     <t>Limpieza</t>
@@ -388,13 +391,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -404,285 +407,100 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
         <v>53.72</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2">
         <v>109.15</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="C3" s="1">
         <v>53.72</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3">
         <v>87.73</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D4">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D5">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D6">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="C7" s="1">
         <v>53.72</v>
       </c>
-      <c r="C4" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>53.72</v>
-      </c>
-      <c r="C5" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>53.72</v>
-      </c>
-      <c r="C6" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>53.72</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="D7">
         <v>86.90000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>53.72</v>
-      </c>
-      <c r="C8" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>53.72</v>
+    <row r="9" spans="1:4">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>53.72</v>
-      </c>
-      <c r="C10" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>53.72</v>
-      </c>
-      <c r="C11" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>53.72</v>
-      </c>
-      <c r="C12" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>53.72</v>
-      </c>
-      <c r="C13" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>53.72</v>
-      </c>
-      <c r="C14" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>53.72</v>
-      </c>
-      <c r="C15" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>53.72</v>
-      </c>
-      <c r="C16" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>53.72</v>
-      </c>
-      <c r="C17" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <v>53.72</v>
-      </c>
-      <c r="C18" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19">
-        <v>53.72</v>
-      </c>
-      <c r="C19" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1311.63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>53.72</v>
-      </c>
-      <c r="C21" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>53.72</v>
-      </c>
-      <c r="C22" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>53.72</v>
-      </c>
-      <c r="C23" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24">
-        <v>53.72</v>
-      </c>
-      <c r="C24" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25">
-        <v>53.72</v>
-      </c>
-      <c r="C25" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26">
-        <v>53.72</v>
-      </c>
-      <c r="C26" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="B28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1">
-        <f>SUM(C2:C26)</f>
+        <f>SUM(C2:C7)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Concepto</t>
   </si>
@@ -47,6 +47,18 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>SUBTOTAL DEL IVA</t>
+  </si>
+  <si>
+    <t>TOTAL SIN IMPUESTOS</t>
+  </si>
+  <si>
+    <t>TOTAL CON IMPUESTOS</t>
   </si>
 </sst>
 </file>
@@ -391,10 +403,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -407,7 +419,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -421,7 +433,7 @@
       <c r="C2" s="1">
         <v>53.72</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>109.15</v>
       </c>
     </row>
@@ -435,7 +447,7 @@
       <c r="C3" s="1">
         <v>53.72</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>87.73</v>
       </c>
     </row>
@@ -449,7 +461,7 @@
       <c r="C4" s="1">
         <v>53.72</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>37.64</v>
       </c>
     </row>
@@ -463,7 +475,7 @@
       <c r="C5" s="1">
         <v>53.72</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>85.91</v>
       </c>
     </row>
@@ -477,7 +489,7 @@
       <c r="C6" s="1">
         <v>53.72</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>29.88</v>
       </c>
     </row>
@@ -491,16 +503,64 @@
       <c r="C7" s="1">
         <v>53.72</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>86.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="B9">
+        <f>SUM(B2:B7)</f>
+        <v>0</v>
       </c>
       <c r="C9" s="1">
         <f>SUM(C2:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <f>SUM(D2:D7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <f>SUM(C9)*0.21</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <f>SUM(D9)*0.21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1">
+        <f>SUM(C10, D10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1">
+        <f>SUM(C9,D9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <f>SUM(D11, D12)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Concepto</t>
   </si>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
@@ -507,60 +507,144 @@
         <v>86.90000000000001</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D8" s="1">
+        <v>109.15</v>
+      </c>
+    </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D9" s="1">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D10" s="1">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D11" s="1">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D12" s="1">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D13" s="1">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <f>SUM(B2:B7)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <f>SUM(C2:C7)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <f>SUM(D2:D7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="B15">
+        <f>SUM(B2:B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <f>SUM(C2:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <f>SUM(D2:D13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1">
-        <f>SUM(C9)*0.21</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <f>SUM(D9)*0.21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="C16" s="1">
+        <f>SUM(C15)*0.21</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <f>SUM(D15)*0.21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1">
-        <f>SUM(C10, D10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="D17" s="1">
+        <f>SUM(C16, D16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="1">
-        <f>SUM(C9,D9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="D18" s="1">
+        <f>SUM(C15,D15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1">
-        <f>SUM(D11, D12)</f>
+      <c r="D19" s="1">
+        <f>SUM(D17, D18)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>Concepto</t>
   </si>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
@@ -591,60 +591,144 @@
         <v>86.90000000000001</v>
       </c>
     </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D14" s="1">
+        <v>109.15</v>
+      </c>
+    </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D15" s="1">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D16" s="1">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D17" s="1">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D18" s="1">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D19" s="1">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B15">
-        <f>SUM(B2:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="1">
-        <f>SUM(C2:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <f>SUM(D2:D13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="B21">
+        <f>SUM(B2:B19)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <f>SUM(C2:C19)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <f>SUM(D2:D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1">
-        <f>SUM(C15)*0.21</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="1">
-        <f>SUM(D15)*0.21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="C22" s="1">
+        <f>SUM(C21)*0.21</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <f>SUM(D21)*0.21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="1">
-        <f>SUM(C16, D16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="D23" s="1">
+        <f>SUM(C22, D22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="1">
-        <f>SUM(C15,D15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="D24" s="1">
+        <f>SUM(C21,D21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="1">
-        <f>SUM(D17, D18)</f>
+      <c r="D25" s="1">
+        <f>SUM(D23, D24)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>Concepto</t>
   </si>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
@@ -675,60 +675,144 @@
         <v>86.90000000000001</v>
       </c>
     </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D20" s="1">
+        <v>109.15</v>
+      </c>
+    </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D21" s="1">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D22" s="1">
+        <v>37.64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D23" s="1">
+        <v>85.91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D24" s="1">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="D25" s="1">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21">
-        <f>SUM(B2:B19)</f>
+      <c r="B27">
+        <f>SUM(B2:B25)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="1">
-        <f>SUM(C2:C19)</f>
+      <c r="C27" s="1">
+        <f>SUM(C2:C25)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="1">
-        <f>SUM(D2:D19)</f>
+      <c r="D27" s="1">
+        <f>SUM(D2:D25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="1">
-        <f>SUM(C21)*0.21</f>
+      <c r="C28" s="1">
+        <f>SUM(C27)*0.21</f>
         <v>0</v>
       </c>
-      <c r="D22" s="1">
-        <f>SUM(D21)*0.21</f>
+      <c r="D28" s="1">
+        <f>SUM(D27)*0.21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="1">
-        <f>SUM(C22, D22)</f>
+      <c r="D29" s="1">
+        <f>SUM(C28, D28)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="1">
-        <f>SUM(C21,D21)</f>
+      <c r="D30" s="1">
+        <f>SUM(C27,D27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="1">
-        <f>SUM(D23, D24)</f>
+      <c r="D31" s="1">
+        <f>SUM(D29, D30)</f>
         <v>0</v>
       </c>
     </row>

--- a/resumen_facturas.xlsx
+++ b/resumen_facturas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Concepto</t>
   </si>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
@@ -508,311 +508,67 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
       <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>53.72</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D9" s="1">
-        <v>87.73</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>6</v>
+      <c r="A10" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <f>SUM(B2:B8)</f>
+        <v>0</v>
       </c>
       <c r="C10" s="1">
-        <v>53.72</v>
+        <f>SUM(C2:C8)</f>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>37.64</v>
+        <f>SUM(D2:D8)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
+      <c r="A11" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C11" s="1">
-        <v>53.72</v>
+        <f>SUM(C10)*0.21</f>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>85.91</v>
+        <f>SUM(D10)*0.21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>53.72</v>
+      <c r="A12" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D12" s="1">
-        <v>29.88</v>
+        <f>SUM(C11, D11)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>53.72</v>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D13" s="1">
-        <v>86.90000000000001</v>
+        <f>SUM(C10,D10)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1">
-        <v>53.72</v>
+      <c r="A14" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D14" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D15" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D16" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D17" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D18" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-      <c r="C19" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D19" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D20" s="1">
-        <v>109.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D21" s="1">
-        <v>87.73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D22" s="1">
-        <v>37.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D23" s="1">
-        <v>85.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D24" s="1">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25" s="1">
-        <v>53.72</v>
-      </c>
-      <c r="D25" s="1">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27">
-        <f>SUM(B2:B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <f>SUM(C2:C25)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="1">
-        <f>SUM(D2:D25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="1">
-        <f>SUM(C27)*0.21</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="1">
-        <f>SUM(D27)*0.21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="1">
-        <f>SUM(C28, D28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="1">
-        <f>SUM(C27,D27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="1">
-        <f>SUM(D29, D30)</f>
+        <f>SUM(D12, D13)</f>
         <v>0</v>
       </c>
     </row>
